--- a/College Track.xlsx
+++ b/College Track.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\College Material\CollegeTrack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College Material\CollegeTrack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA83CE7-EF42-4576-8E2E-48063EAA3880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7BF552-BBD0-4620-B3F5-7CA74E9783C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1A41BE31-1ECF-4A76-AA25-4685734A5295}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="199">
   <si>
     <t>Fall 2022</t>
   </si>
@@ -640,6 +640,24 @@
   </si>
   <si>
     <t>C+</t>
+  </si>
+  <si>
+    <t>Spring 2026</t>
+  </si>
+  <si>
+    <t>Project II</t>
+  </si>
+  <si>
+    <t>Game Design &amp; Modeling</t>
+  </si>
+  <si>
+    <t>User Interface Design</t>
+  </si>
+  <si>
+    <t>Data structures</t>
+  </si>
+  <si>
+    <t>Information Retrieval</t>
   </si>
 </sst>
 </file>
@@ -928,7 +946,70 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="278">
+  <dxfs count="303">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0000000"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1788,6 +1869,37 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="0000000"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2138,336 +2250,339 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EC8BBAC2-F974-41EE-A33B-D9728D1FB776}" name="Table1" displayName="Table1" ref="B4:H12" totalsRowShown="0" headerRowDxfId="277" dataDxfId="276">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EC8BBAC2-F974-41EE-A33B-D9728D1FB776}" name="Table1" displayName="Table1" ref="B4:H12" totalsRowShown="0" headerRowDxfId="302" dataDxfId="301">
   <autoFilter ref="B4:H12" xr:uid="{EC8BBAC2-F974-41EE-A33B-D9728D1FB776}"/>
   <tableColumns count="7">
-    <tableColumn id="8" xr3:uid="{63F333E7-F6E7-4DF2-9487-C123CB920E95}" name="C. No" dataDxfId="275"/>
-    <tableColumn id="9" xr3:uid="{F38EB66C-1B09-4660-BFC2-9DB78AF36267}" name="Course Name" dataDxfId="274"/>
-    <tableColumn id="15" xr3:uid="{12EB338E-68DD-4BC0-95B6-BCEDDA4E9521}" name="Pre-Requisite" dataDxfId="273"/>
-    <tableColumn id="10" xr3:uid="{E33BFB61-8B17-4729-87F1-6D2275CF5C92}" name="Course Code" dataDxfId="272"/>
-    <tableColumn id="11" xr3:uid="{756EBA51-EBAD-43CF-A483-1C218FFC4EBC}" name="Credit Hours" dataDxfId="271"/>
-    <tableColumn id="12" xr3:uid="{2076F066-C303-420A-8C33-F20C8697EE39}" name="Credit Hour Price" dataDxfId="270"/>
-    <tableColumn id="13" xr3:uid="{AC87CA98-BDD2-4601-8551-394BD3998015}" name="Course Price" dataDxfId="269"/>
+    <tableColumn id="8" xr3:uid="{63F333E7-F6E7-4DF2-9487-C123CB920E95}" name="C. No" dataDxfId="300"/>
+    <tableColumn id="9" xr3:uid="{F38EB66C-1B09-4660-BFC2-9DB78AF36267}" name="Course Name" dataDxfId="299"/>
+    <tableColumn id="15" xr3:uid="{12EB338E-68DD-4BC0-95B6-BCEDDA4E9521}" name="Pre-Requisite" dataDxfId="298"/>
+    <tableColumn id="10" xr3:uid="{E33BFB61-8B17-4729-87F1-6D2275CF5C92}" name="Course Code" dataDxfId="297"/>
+    <tableColumn id="11" xr3:uid="{756EBA51-EBAD-43CF-A483-1C218FFC4EBC}" name="Credit Hours" dataDxfId="296"/>
+    <tableColumn id="12" xr3:uid="{2076F066-C303-420A-8C33-F20C8697EE39}" name="Credit Hour Price" dataDxfId="295"/>
+    <tableColumn id="13" xr3:uid="{AC87CA98-BDD2-4601-8551-394BD3998015}" name="Course Price" dataDxfId="294"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{96D8E5AD-210F-4754-8120-BE78EBD354EC}" name="Table6" displayName="Table6" ref="B26:F33" totalsRowShown="0" dataDxfId="153">
-  <autoFilter ref="B26:F33" xr:uid="{96D8E5AD-210F-4754-8120-BE78EBD354EC}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{28F8E7D6-B383-4600-A048-22F8C4AD82D6}" name="S. No" dataDxfId="152"/>
-    <tableColumn id="2" xr3:uid="{98B567B0-0A0B-437E-A58C-5F6D5BF775AD}" name="Course Name" dataDxfId="151"/>
-    <tableColumn id="6" xr3:uid="{BE62E445-155B-4DCE-9238-BB400FE31908}" name="Midterm" dataDxfId="150"/>
-    <tableColumn id="7" xr3:uid="{C3F1662F-2159-423B-907C-383464F612E9}" name="Pre-Final" dataDxfId="149"/>
-    <tableColumn id="3" xr3:uid="{176A7C21-7E63-40F2-B1DC-6AF4F5AA9C6A}" name="Final" dataDxfId="148"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{70147C35-1E51-4E8F-8D2F-0DC595D09A6B}" name="Table35" displayName="Table35" ref="B15:H22" totalsRowShown="0" dataDxfId="176">
+  <autoFilter ref="B15:H22" xr:uid="{70147C35-1E51-4E8F-8D2F-0DC595D09A6B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{02190C55-16B9-496A-8C2B-E2D76168AF93}" name="S. No" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{8DDC9744-D783-4D5E-B711-CF5C3C040ABC}" name="Course Name" dataDxfId="174"/>
+    <tableColumn id="4" xr3:uid="{34FCA559-C89D-473C-8942-2292B887A2A4}" name="Midterm" dataDxfId="173"/>
+    <tableColumn id="11" xr3:uid="{26BFE13A-C341-4990-AFFA-A6ECAD09F356}" name="Pre-Final" dataDxfId="172"/>
+    <tableColumn id="12" xr3:uid="{BCC3D8B0-331D-4A91-B469-53D9E53C629B}" name="Final" dataDxfId="171"/>
+    <tableColumn id="3" xr3:uid="{AAF2F08F-0FFC-4D29-8E35-7A389C090684}" name="Bonus" dataDxfId="170"/>
+    <tableColumn id="5" xr3:uid="{6B12A4D2-2FF5-4394-9DE7-26EFEC40F165}" name="Project" dataDxfId="169"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DE3B1C29-A03B-46CD-A952-A7C9318DF265}" name="Table616" displayName="Table616" ref="B37:F43" totalsRowShown="0" dataDxfId="147">
-  <autoFilter ref="B37:F43" xr:uid="{DE3B1C29-A03B-46CD-A952-A7C9318DF265}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{96D8E5AD-210F-4754-8120-BE78EBD354EC}" name="Table6" displayName="Table6" ref="B26:F33" totalsRowShown="0" dataDxfId="168">
+  <autoFilter ref="B26:F33" xr:uid="{96D8E5AD-210F-4754-8120-BE78EBD354EC}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4F82C258-BC76-45EB-AB03-0254FCD1BA9C}" name="S. No" dataDxfId="146"/>
-    <tableColumn id="2" xr3:uid="{1931576C-90BA-4965-A648-CB87B1A01E8B}" name="Course Name" dataDxfId="145"/>
-    <tableColumn id="6" xr3:uid="{08710819-4BB9-4191-AE7E-B6B02498EA38}" name="Midterm" dataDxfId="144"/>
-    <tableColumn id="7" xr3:uid="{8B347F23-C206-4753-B777-B4A4BE2F85A1}" name="Pre-Final" dataDxfId="143"/>
-    <tableColumn id="3" xr3:uid="{CF91586C-C31D-4CEC-AFD8-249AEAC0B6B5}" name="Final" dataDxfId="142"/>
+    <tableColumn id="1" xr3:uid="{28F8E7D6-B383-4600-A048-22F8C4AD82D6}" name="S. No" dataDxfId="167"/>
+    <tableColumn id="2" xr3:uid="{98B567B0-0A0B-437E-A58C-5F6D5BF775AD}" name="Course Name" dataDxfId="166"/>
+    <tableColumn id="6" xr3:uid="{BE62E445-155B-4DCE-9238-BB400FE31908}" name="Midterm" dataDxfId="165"/>
+    <tableColumn id="7" xr3:uid="{C3F1662F-2159-423B-907C-383464F612E9}" name="Pre-Final" dataDxfId="164"/>
+    <tableColumn id="3" xr3:uid="{176A7C21-7E63-40F2-B1DC-6AF4F5AA9C6A}" name="Final" dataDxfId="163"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A6024FA2-2C7E-4A52-B4CF-61F7EEC022F9}" name="Table61624" displayName="Table61624" ref="B47:H53" totalsRowShown="0" dataDxfId="141">
-  <autoFilter ref="B47:H53" xr:uid="{A6024FA2-2C7E-4A52-B4CF-61F7EEC022F9}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F0565AE4-0C5A-4BA4-81C1-C3BF63F38597}" name="S. No" dataDxfId="140"/>
-    <tableColumn id="2" xr3:uid="{70A028AD-DF2A-4E5E-9621-DA8238901B60}" name="Course Name" dataDxfId="139"/>
-    <tableColumn id="4" xr3:uid="{F4AC14A7-22C6-4923-9435-8AD07D827C2E}" name="Midterm" dataDxfId="138"/>
-    <tableColumn id="6" xr3:uid="{39F5F465-4349-4266-9CE6-EAD28560B5D5}" name="Midterm Max" dataDxfId="137"/>
-    <tableColumn id="5" xr3:uid="{0372BF70-7A21-4D25-B7A9-143A246B4128}" name="Pre-Final" dataDxfId="136">
-      <calculatedColumnFormula array="1">Table61624[[#This Row],[Midterm]]+Table1012172213[Total]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{6A531446-7626-4D12-95D3-566FCDECDE06}" name="Pre-Final Max" dataDxfId="135"/>
-    <tableColumn id="3" xr3:uid="{7023FDA4-15BC-44F7-9AAE-FFA2941DBFEA}" name="Final" dataDxfId="134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{DE3B1C29-A03B-46CD-A952-A7C9318DF265}" name="Table616" displayName="Table616" ref="B37:F43" totalsRowShown="0" dataDxfId="162">
+  <autoFilter ref="B37:F43" xr:uid="{DE3B1C29-A03B-46CD-A952-A7C9318DF265}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{4F82C258-BC76-45EB-AB03-0254FCD1BA9C}" name="S. No" dataDxfId="161"/>
+    <tableColumn id="2" xr3:uid="{1931576C-90BA-4965-A648-CB87B1A01E8B}" name="Course Name" dataDxfId="160"/>
+    <tableColumn id="6" xr3:uid="{08710819-4BB9-4191-AE7E-B6B02498EA38}" name="Midterm" dataDxfId="159"/>
+    <tableColumn id="7" xr3:uid="{8B347F23-C206-4753-B777-B4A4BE2F85A1}" name="Pre-Final" dataDxfId="158"/>
+    <tableColumn id="3" xr3:uid="{CF91586C-C31D-4CEC-AFD8-249AEAC0B6B5}" name="Final" dataDxfId="157"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{370E7FB4-8BC2-4CA7-AD18-062C08A5094F}" name="Table6162430" displayName="Table6162430" ref="B57:H64" totalsRowShown="0" dataDxfId="133">
-  <autoFilter ref="B57:H64" xr:uid="{370E7FB4-8BC2-4CA7-AD18-062C08A5094F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A6024FA2-2C7E-4A52-B4CF-61F7EEC022F9}" name="Table61624" displayName="Table61624" ref="B47:H53" totalsRowShown="0" dataDxfId="156">
+  <autoFilter ref="B47:H53" xr:uid="{A6024FA2-2C7E-4A52-B4CF-61F7EEC022F9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{874C6CE1-BE37-4065-8A5B-CECA185231DD}" name="S. No" dataDxfId="132"/>
-    <tableColumn id="2" xr3:uid="{1A6EF9CF-36EA-4225-8EDC-59E8261EE8ED}" name="Course Name" dataDxfId="131"/>
-    <tableColumn id="4" xr3:uid="{8DCECEC6-AF29-4448-A504-394C4F78710B}" name="Midterm" dataDxfId="130"/>
-    <tableColumn id="6" xr3:uid="{A777B523-E7AD-4B84-A6C4-E17D9A3BFEC2}" name="Midterm Max" dataDxfId="129"/>
-    <tableColumn id="5" xr3:uid="{7AB0F2C2-2B49-45C4-A8FE-2C45A511D90E}" name="Pre-Final" dataDxfId="128"/>
-    <tableColumn id="7" xr3:uid="{7ECD9B0F-32A7-4470-9AE8-F31CD77EEF31}" name="Pre-Final Max" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{3FB56E3B-E7C4-45EC-843B-E1B1C506C2C2}" name="Final" dataDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{F0565AE4-0C5A-4BA4-81C1-C3BF63F38597}" name="S. No" dataDxfId="155"/>
+    <tableColumn id="2" xr3:uid="{70A028AD-DF2A-4E5E-9621-DA8238901B60}" name="Course Name" dataDxfId="154"/>
+    <tableColumn id="4" xr3:uid="{F4AC14A7-22C6-4923-9435-8AD07D827C2E}" name="Midterm" dataDxfId="153"/>
+    <tableColumn id="6" xr3:uid="{39F5F465-4349-4266-9CE6-EAD28560B5D5}" name="Midterm Max" dataDxfId="152"/>
+    <tableColumn id="5" xr3:uid="{0372BF70-7A21-4D25-B7A9-143A246B4128}" name="Pre-Final" dataDxfId="151">
+      <calculatedColumnFormula array="1">Table61624[[#This Row],[Midterm]]+Table1012172213[Total]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{6A531446-7626-4D12-95D3-566FCDECDE06}" name="Pre-Final Max" dataDxfId="150"/>
+    <tableColumn id="3" xr3:uid="{7023FDA4-15BC-44F7-9AAE-FFA2941DBFEA}" name="Final" dataDxfId="149"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{9F1265F9-AB4C-4B22-AFB0-990D7FB11370}" name="Table6162432" displayName="Table6162432" ref="B68:H74" totalsRowShown="0" dataDxfId="125">
-  <autoFilter ref="B68:H74" xr:uid="{9F1265F9-AB4C-4B22-AFB0-990D7FB11370}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{370E7FB4-8BC2-4CA7-AD18-062C08A5094F}" name="Table6162430" displayName="Table6162430" ref="B57:H64" totalsRowShown="0" dataDxfId="148">
+  <autoFilter ref="B57:H64" xr:uid="{370E7FB4-8BC2-4CA7-AD18-062C08A5094F}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{664F5CDF-4D5A-4AB9-B0DF-D46C4C6C47DB}" name="S. No" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{5D5952DD-D5D0-48D8-A09A-5C3787458452}" name="Course Name" dataDxfId="123"/>
-    <tableColumn id="4" xr3:uid="{800C8597-AB8E-4449-AAE2-D7F96AE010DD}" name="Midterm" dataDxfId="122"/>
-    <tableColumn id="6" xr3:uid="{0667FBFF-BCB5-4FDD-95B4-B91507465F57}" name="Midterm Max" dataDxfId="121"/>
-    <tableColumn id="5" xr3:uid="{52418EF3-8193-4EB3-90FB-02AE47ECB9EE}" name="Pre-Final" dataDxfId="120"/>
-    <tableColumn id="7" xr3:uid="{120A9349-EEB9-4906-9E72-9E47824D513B}" name="Pre-Final Max" dataDxfId="119"/>
-    <tableColumn id="3" xr3:uid="{2ED418C5-DB56-49D5-ABE8-E141913E6CCD}" name="Final" dataDxfId="118"/>
+    <tableColumn id="1" xr3:uid="{874C6CE1-BE37-4065-8A5B-CECA185231DD}" name="S. No" dataDxfId="147"/>
+    <tableColumn id="2" xr3:uid="{1A6EF9CF-36EA-4225-8EDC-59E8261EE8ED}" name="Course Name" dataDxfId="146"/>
+    <tableColumn id="4" xr3:uid="{8DCECEC6-AF29-4448-A504-394C4F78710B}" name="Midterm" dataDxfId="145"/>
+    <tableColumn id="6" xr3:uid="{A777B523-E7AD-4B84-A6C4-E17D9A3BFEC2}" name="Midterm Max" dataDxfId="144"/>
+    <tableColumn id="5" xr3:uid="{7AB0F2C2-2B49-45C4-A8FE-2C45A511D90E}" name="Pre-Final" dataDxfId="143"/>
+    <tableColumn id="7" xr3:uid="{7ECD9B0F-32A7-4470-9AE8-F31CD77EEF31}" name="Pre-Final Max" dataDxfId="142"/>
+    <tableColumn id="3" xr3:uid="{3FB56E3B-E7C4-45EC-843B-E1B1C506C2C2}" name="Final" dataDxfId="141"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EFA08C7C-68AF-4708-93FB-8A290D3CB387}" name="Table8" displayName="Table8" ref="B5:I6" totalsRowShown="0" headerRowDxfId="117" dataDxfId="116">
-  <autoFilter ref="B5:I6" xr:uid="{EFA08C7C-68AF-4708-93FB-8A290D3CB387}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D1D035A0-8468-4A7F-BBC8-CFCD96813B23}" name="Multimedia Systems" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{F67BEE79-F853-45BF-ACC7-46967A79CC91}" name="Tasks" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{C5E6CA24-CF22-43DE-85B3-B617638899F8}" name="Project 1" dataDxfId="113"/>
-    <tableColumn id="4" xr3:uid="{CE096E8B-0AE9-44EE-B92F-A2252BD19F8C}" name="Bonus" dataDxfId="112"/>
-    <tableColumn id="7" xr3:uid="{31FCDAB2-1D09-4A11-9E1A-B2CD4AF7F500}" name="Attendance" dataDxfId="111"/>
-    <tableColumn id="8" xr3:uid="{94F7195F-14BE-405B-A2B6-09558AF95CE3}" name="Project 2" dataDxfId="110"/>
-    <tableColumn id="5" xr3:uid="{52A7195C-5714-4061-AC64-56C2AAB3A983}" name="Projects" dataDxfId="109"/>
-    <tableColumn id="6" xr3:uid="{F81B11B2-B747-4E38-8D17-165EDC9C5B68}" name="Total2" dataDxfId="108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{9F1265F9-AB4C-4B22-AFB0-990D7FB11370}" name="Table6162432" displayName="Table6162432" ref="B68:H74" totalsRowShown="0" dataDxfId="140">
+  <autoFilter ref="B68:H74" xr:uid="{9F1265F9-AB4C-4B22-AFB0-990D7FB11370}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{664F5CDF-4D5A-4AB9-B0DF-D46C4C6C47DB}" name="S. No" dataDxfId="139"/>
+    <tableColumn id="2" xr3:uid="{5D5952DD-D5D0-48D8-A09A-5C3787458452}" name="Course Name" dataDxfId="138"/>
+    <tableColumn id="4" xr3:uid="{800C8597-AB8E-4449-AAE2-D7F96AE010DD}" name="Midterm" dataDxfId="137"/>
+    <tableColumn id="6" xr3:uid="{0667FBFF-BCB5-4FDD-95B4-B91507465F57}" name="Midterm Max" dataDxfId="136"/>
+    <tableColumn id="5" xr3:uid="{52418EF3-8193-4EB3-90FB-02AE47ECB9EE}" name="Pre-Final" dataDxfId="135"/>
+    <tableColumn id="7" xr3:uid="{120A9349-EEB9-4906-9E72-9E47824D513B}" name="Pre-Final Max" dataDxfId="134"/>
+    <tableColumn id="3" xr3:uid="{2ED418C5-DB56-49D5-ABE8-E141913E6CCD}" name="Final" dataDxfId="133"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{942B0E4B-DB7B-46E3-AC4A-31C65CC8220C}" name="Table9" displayName="Table9" ref="B9:F10" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
-  <autoFilter ref="B9:F10" xr:uid="{942B0E4B-DB7B-46E3-AC4A-31C65CC8220C}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{700B3547-6D3B-4765-A5E4-AC07353FFE64}" name="Software Engineering Theory" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{C9951BA9-3C1D-49EF-830C-D48C1BEEC830}" name="Presentation&amp;Assignments" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{E647E6EE-A073-4519-87D8-02044BBC6F98}" name="Project" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{F2D93F54-8EAD-4ED9-87AE-E37C13C3187F}" name="Bonus" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{2C44B120-1098-4D7D-BF6F-BF2542B03382}" name="Total" dataDxfId="101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{7EFD9C7A-E5FF-4166-BD69-96023505CC19}" name="Table616243234" displayName="Table616243234" ref="B78:H82" totalsRowShown="0" dataDxfId="14">
+  <autoFilter ref="B78:H82" xr:uid="{7EFD9C7A-E5FF-4166-BD69-96023505CC19}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{970061A5-6591-4493-BCD7-E7E806E925E0}" name="S. No" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{8321E3E8-3F3F-4868-A7A8-E34A3ABE8426}" name="Course Name" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{DCA51AA1-E7E6-4834-8405-645615EB405E}" name="Midterm" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F72F8183-57BA-415D-9D5E-27D0BDAF5E5A}" name="Midterm Max" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{248FFDD4-C36D-43DF-BA7F-4F1EA6600E2B}" name="Pre-Final" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{BD9F4F85-7C9D-4D56-B1A6-AA33A0CC86F2}" name="Pre-Final Max" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B417FB7E-1DE9-400F-B0BA-60D9DFBC0B8D}" name="Final" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{EE574216-6034-48AC-935F-4B51B28B2F02}" name="Table10" displayName="Table10" ref="B13:C14" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99">
-  <autoFilter ref="B13:C14" xr:uid="{EE574216-6034-48AC-935F-4B51B28B2F02}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{FB6AF181-FD31-4972-85B7-B738A5302BA5}" name="Maths III" dataDxfId="98"/>
-    <tableColumn id="2" xr3:uid="{2776461E-0EFC-42E5-83DD-8C7E8528663B}" name="Quizes" dataDxfId="97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EFA08C7C-68AF-4708-93FB-8A290D3CB387}" name="Table8" displayName="Table8" ref="B5:I6" totalsRowShown="0" headerRowDxfId="132" dataDxfId="131">
+  <autoFilter ref="B5:I6" xr:uid="{EFA08C7C-68AF-4708-93FB-8A290D3CB387}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D1D035A0-8468-4A7F-BBC8-CFCD96813B23}" name="Multimedia Systems" dataDxfId="130"/>
+    <tableColumn id="2" xr3:uid="{F67BEE79-F853-45BF-ACC7-46967A79CC91}" name="Tasks" dataDxfId="129"/>
+    <tableColumn id="3" xr3:uid="{C5E6CA24-CF22-43DE-85B3-B617638899F8}" name="Project 1" dataDxfId="128"/>
+    <tableColumn id="4" xr3:uid="{CE096E8B-0AE9-44EE-B92F-A2252BD19F8C}" name="Bonus" dataDxfId="127"/>
+    <tableColumn id="7" xr3:uid="{31FCDAB2-1D09-4A11-9E1A-B2CD4AF7F500}" name="Attendance" dataDxfId="126"/>
+    <tableColumn id="8" xr3:uid="{94F7195F-14BE-405B-A2B6-09558AF95CE3}" name="Project 2" dataDxfId="125"/>
+    <tableColumn id="5" xr3:uid="{52A7195C-5714-4061-AC64-56C2AAB3A983}" name="Projects" dataDxfId="124"/>
+    <tableColumn id="6" xr3:uid="{F81B11B2-B747-4E38-8D17-165EDC9C5B68}" name="Total2" dataDxfId="123"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{3F774BB9-9658-4138-A855-7BD586FAC1E9}" name="Table1012" displayName="Table1012" ref="B17:C18" totalsRowShown="0" headerRowDxfId="96" dataDxfId="95">
-  <autoFilter ref="B17:C18" xr:uid="{3F774BB9-9658-4138-A855-7BD586FAC1E9}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{33428839-BE00-405F-9EFD-BBE0568E2A50}" name="Game Programming" dataDxfId="94"/>
-    <tableColumn id="2" xr3:uid="{3EF9BDEC-F6DE-419C-82EF-18636B80F540}" name="Project" dataDxfId="93"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{942B0E4B-DB7B-46E3-AC4A-31C65CC8220C}" name="Table9" displayName="Table9" ref="B9:F10" totalsRowShown="0" headerRowDxfId="122" dataDxfId="121">
+  <autoFilter ref="B9:F10" xr:uid="{942B0E4B-DB7B-46E3-AC4A-31C65CC8220C}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{700B3547-6D3B-4765-A5E4-AC07353FFE64}" name="Software Engineering Theory" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{C9951BA9-3C1D-49EF-830C-D48C1BEEC830}" name="Presentation&amp;Assignments" dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{E647E6EE-A073-4519-87D8-02044BBC6F98}" name="Project" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{F2D93F54-8EAD-4ED9-87AE-E37C13C3187F}" name="Bonus" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{2C44B120-1098-4D7D-BF6F-BF2542B03382}" name="Total" dataDxfId="116"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{205B07DD-0913-424E-A634-CD0EC5EED651}" name="Table10121314" displayName="Table10121314" ref="B21:F22" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
-  <autoFilter ref="B21:F22" xr:uid="{205B07DD-0913-424E-A634-CD0EC5EED651}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D13213E2-B9FE-49ED-A2E5-13C00C70344C}" name="Data Structures" dataDxfId="90"/>
-    <tableColumn id="2" xr3:uid="{643FCD96-8371-4D07-98EB-5BE319409B38}" name="Quizes" dataDxfId="89"/>
-    <tableColumn id="3" xr3:uid="{4D3F7FF1-2E45-4C42-8083-75A4C9E67D00}" name="Attendance" dataDxfId="88"/>
-    <tableColumn id="4" xr3:uid="{0B5A6AB0-906B-4082-8488-F9B2849D3D26}" name="Assignments" dataDxfId="87"/>
-    <tableColumn id="5" xr3:uid="{CFB73E2E-4C15-455B-9767-60198BF30E91}" name="Report" dataDxfId="86"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{EE574216-6034-48AC-935F-4B51B28B2F02}" name="Table10" displayName="Table10" ref="B13:C14" totalsRowShown="0" headerRowDxfId="115" dataDxfId="114">
+  <autoFilter ref="B13:C14" xr:uid="{EE574216-6034-48AC-935F-4B51B28B2F02}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{FB6AF181-FD31-4972-85B7-B738A5302BA5}" name="Maths III" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{2776461E-0EFC-42E5-83DD-8C7E8528663B}" name="Quizes" dataDxfId="112"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCE949A3-1104-4EE3-8974-CAF899620CD7}" name="Table13" displayName="Table13" ref="B15:H23" totalsRowCount="1" headerRowDxfId="268" dataDxfId="267" totalsRowDxfId="266">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCE949A3-1104-4EE3-8974-CAF899620CD7}" name="Table13" displayName="Table13" ref="B15:H23" totalsRowCount="1" headerRowDxfId="293" dataDxfId="292" totalsRowDxfId="291">
   <autoFilter ref="B15:H22" xr:uid="{DCE949A3-1104-4EE3-8974-CAF899620CD7}"/>
   <tableColumns count="7">
-    <tableColumn id="8" xr3:uid="{1863A1F8-44C1-4DCA-BD68-EBFB7384951C}" name="C. No" dataDxfId="265" totalsRowDxfId="264"/>
-    <tableColumn id="9" xr3:uid="{5D3BC791-397A-48D3-BFA5-BBBC1A2A7907}" name="Course Name" dataDxfId="263" totalsRowDxfId="262"/>
-    <tableColumn id="15" xr3:uid="{453A42BC-A072-42B3-8A09-4E6B76DEDCED}" name="Pre-Requisite" dataDxfId="261" totalsRowDxfId="260"/>
-    <tableColumn id="10" xr3:uid="{1700FAE5-8654-46A4-A039-AFBE529992BE}" name="Course Code" dataDxfId="259" totalsRowDxfId="258"/>
-    <tableColumn id="11" xr3:uid="{172877EC-7A8C-4D10-8BC7-342C3D021671}" name="Credit Hours" dataDxfId="257" totalsRowDxfId="256"/>
-    <tableColumn id="12" xr3:uid="{7E6011B4-7A10-4A16-9E75-C91E0A9DED0C}" name="Credit Hour Price" dataDxfId="255" totalsRowDxfId="254"/>
-    <tableColumn id="13" xr3:uid="{920FA2B5-9D44-44C3-BEDA-BA8CE63644C3}" name="Course Price" totalsRowFunction="sum" dataDxfId="253" totalsRowDxfId="252"/>
+    <tableColumn id="8" xr3:uid="{1863A1F8-44C1-4DCA-BD68-EBFB7384951C}" name="C. No" dataDxfId="290" totalsRowDxfId="289"/>
+    <tableColumn id="9" xr3:uid="{5D3BC791-397A-48D3-BFA5-BBBC1A2A7907}" name="Course Name" dataDxfId="288" totalsRowDxfId="287"/>
+    <tableColumn id="15" xr3:uid="{453A42BC-A072-42B3-8A09-4E6B76DEDCED}" name="Pre-Requisite" dataDxfId="286" totalsRowDxfId="285"/>
+    <tableColumn id="10" xr3:uid="{1700FAE5-8654-46A4-A039-AFBE529992BE}" name="Course Code" dataDxfId="284" totalsRowDxfId="283"/>
+    <tableColumn id="11" xr3:uid="{172877EC-7A8C-4D10-8BC7-342C3D021671}" name="Credit Hours" dataDxfId="282" totalsRowDxfId="281"/>
+    <tableColumn id="12" xr3:uid="{7E6011B4-7A10-4A16-9E75-C91E0A9DED0C}" name="Credit Hour Price" dataDxfId="280" totalsRowDxfId="279"/>
+    <tableColumn id="13" xr3:uid="{920FA2B5-9D44-44C3-BEDA-BA8CE63644C3}" name="Course Price" totalsRowFunction="sum" dataDxfId="278" totalsRowDxfId="277"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B4CCA43B-54CF-4907-BD43-87DB602F91D9}" name="Table101217" displayName="Table101217" ref="B29:E30" totalsRowShown="0" headerRowDxfId="85" dataDxfId="84">
-  <autoFilter ref="B29:E30" xr:uid="{B4CCA43B-54CF-4907-BD43-87DB602F91D9}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8D9EF0C0-1B3E-4863-8BAF-044C59C9A388}" name="Web Programming" dataDxfId="83"/>
-    <tableColumn id="2" xr3:uid="{AE418BE6-92BC-432F-9F67-196A7F9940EF}" name="Project" dataDxfId="82"/>
-    <tableColumn id="3" xr3:uid="{D4EC974C-3393-48D5-B53E-585F3D0D1997}" name="Sections" dataDxfId="81"/>
-    <tableColumn id="4" xr3:uid="{E33770EB-3DDD-4D63-94FA-A598B90F5B67}" name="Bonus" dataDxfId="80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{3F774BB9-9658-4138-A855-7BD586FAC1E9}" name="Table1012" displayName="Table1012" ref="B17:C18" totalsRowShown="0" headerRowDxfId="111" dataDxfId="110">
+  <autoFilter ref="B17:C18" xr:uid="{3F774BB9-9658-4138-A855-7BD586FAC1E9}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{33428839-BE00-405F-9EFD-BBE0568E2A50}" name="Game Programming" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{3EF9BDEC-F6DE-419C-82EF-18636B80F540}" name="Project" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{18085C60-6932-4B11-8EB0-1CD628F08C0F}" name="Table10121718" displayName="Table10121718" ref="B33:D34" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
-  <autoFilter ref="B33:D34" xr:uid="{18085C60-6932-4B11-8EB0-1CD628F08C0F}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B12A5AD3-F7F5-4108-BCE4-51518FCFC4E4}" name="Database" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{8DFA2315-436C-47E5-BC83-BF1E161BAC8D}" name="ERD &amp; Business Rules" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{0B716030-3726-45F6-9CBF-54A88D8F5F46}" name="SQL" dataDxfId="75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{205B07DD-0913-424E-A634-CD0EC5EED651}" name="Table10121314" displayName="Table10121314" ref="B21:F22" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
+  <autoFilter ref="B21:F22" xr:uid="{205B07DD-0913-424E-A634-CD0EC5EED651}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D13213E2-B9FE-49ED-A2E5-13C00C70344C}" name="Data Structures" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{643FCD96-8371-4D07-98EB-5BE319409B38}" name="Quizes" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{4D3F7FF1-2E45-4C42-8083-75A4C9E67D00}" name="Attendance" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{0B5A6AB0-906B-4082-8488-F9B2849D3D26}" name="Assignments" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{CFB73E2E-4C15-455B-9767-60198BF30E91}" name="Report" dataDxfId="101"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{EEF6F50E-25FF-40F6-81C5-73210378FB38}" name="Table10121719" displayName="Table10121719" ref="B37:G38" totalsRowShown="0" headerRowDxfId="74" dataDxfId="73">
-  <autoFilter ref="B37:G38" xr:uid="{EEF6F50E-25FF-40F6-81C5-73210378FB38}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A927A777-891A-459A-B181-D3F12121968A}" name="HCI" dataDxfId="72"/>
-    <tableColumn id="2" xr3:uid="{79EAEA15-A950-4644-BAC9-5F313DE31336}" name="Persona &amp; Comp. Research" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{38B85951-D9A2-40C7-A404-E6D3FAC57915}" name="User Flow &amp; Sketching" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{9A317C4B-A29C-447E-81E3-B9999A6E82CB}" name="Wireframe" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{7F815F66-3A06-49CE-B7D6-F50614693D29}" name="Protoype" dataDxfId="68"/>
-    <tableColumn id="6" xr3:uid="{FCD0A372-08B9-4F5C-A6F6-69F4B9E5B973}" name="Mouse Cursor Project" dataDxfId="67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{B4CCA43B-54CF-4907-BD43-87DB602F91D9}" name="Table101217" displayName="Table101217" ref="B29:E30" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99">
+  <autoFilter ref="B29:E30" xr:uid="{B4CCA43B-54CF-4907-BD43-87DB602F91D9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{8D9EF0C0-1B3E-4863-8BAF-044C59C9A388}" name="Web Programming" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{AE418BE6-92BC-432F-9F67-196A7F9940EF}" name="Project" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{D4EC974C-3393-48D5-B53E-585F3D0D1997}" name="Sections" dataDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{E33770EB-3DDD-4D63-94FA-A598B90F5B67}" name="Bonus" dataDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{65C1972D-B50E-43C0-802E-2C46885C0F00}" name="Table10121720" displayName="Table10121720" ref="B41:E42" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
-  <autoFilter ref="B41:E42" xr:uid="{65C1972D-B50E-43C0-802E-2C46885C0F00}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{035A81E6-D0E9-4514-856A-4268F8CC9DA6}" name="SWRA" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{12D2C635-A485-47AD-8190-8C54FBF9000C}" name="Project" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{45F2C637-AC09-44A5-92E8-6BADCFC9B3F1}" name="Tasks" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{8FA9D5CD-8C7B-4804-B737-1E714122E0BB}" name="Bonus" dataDxfId="61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{18085C60-6932-4B11-8EB0-1CD628F08C0F}" name="Table10121718" displayName="Table10121718" ref="B33:D34" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
+  <autoFilter ref="B33:D34" xr:uid="{18085C60-6932-4B11-8EB0-1CD628F08C0F}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{B12A5AD3-F7F5-4108-BCE4-51518FCFC4E4}" name="Database" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{8DFA2315-436C-47E5-BC83-BF1E161BAC8D}" name="ERD &amp; Business Rules" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{0B716030-3726-45F6-9CBF-54A88D8F5F46}" name="SQL" dataDxfId="90"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{0C386865-EF18-4181-8C7E-093B513259C4}" name="Table10121721" displayName="Table10121721" ref="B45:G46" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
-  <autoFilter ref="B45:G46" xr:uid="{0C386865-EF18-4181-8C7E-093B513259C4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{EEF6F50E-25FF-40F6-81C5-73210378FB38}" name="Table10121719" displayName="Table10121719" ref="B37:G38" totalsRowShown="0" headerRowDxfId="89" dataDxfId="88">
+  <autoFilter ref="B37:G38" xr:uid="{EEF6F50E-25FF-40F6-81C5-73210378FB38}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{42FC35EA-B43D-48B3-B3A3-595F88F92450}" name="Data Mining" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{9FEB74EB-AC46-401B-BB9E-8C8A45D5AF88}" name="Quiz" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{8B9598E1-5543-4747-9C5F-C4096AAF4F60}" name="Assignment 1" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{891DC4A3-A6EA-4A59-BA25-7BA469C2BB0A}" name="Assignment 2" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{758071D9-C1B0-45BD-B6BF-33C3918898F3}" name="Quiz 2" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{343E6371-5E31-41BB-B2F7-397D9E50F2F8}" name="Total" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{A927A777-891A-459A-B181-D3F12121968A}" name="HCI" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{79EAEA15-A950-4644-BAC9-5F313DE31336}" name="Persona &amp; Comp. Research" dataDxfId="86"/>
+    <tableColumn id="3" xr3:uid="{38B85951-D9A2-40C7-A404-E6D3FAC57915}" name="User Flow &amp; Sketching" dataDxfId="85"/>
+    <tableColumn id="4" xr3:uid="{9A317C4B-A29C-447E-81E3-B9999A6E82CB}" name="Wireframe" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{7F815F66-3A06-49CE-B7D6-F50614693D29}" name="Protoype" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{FCD0A372-08B9-4F5C-A6F6-69F4B9E5B973}" name="Mouse Cursor Project" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{7E679E8C-B166-4F68-9A53-21A0412D5E9D}" name="Table10121722" displayName="Table10121722" ref="B49:C50" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
-  <autoFilter ref="B49:C50" xr:uid="{7E679E8C-B166-4F68-9A53-21A0412D5E9D}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{62817289-D4F9-4533-A45B-83BD78F1E21D}" name="Maths IV" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{85694941-D6AA-4481-BDF5-36CF8B4AE004}" name="Quiz" dataDxfId="49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{65C1972D-B50E-43C0-802E-2C46885C0F00}" name="Table10121720" displayName="Table10121720" ref="B41:E42" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+  <autoFilter ref="B41:E42" xr:uid="{65C1972D-B50E-43C0-802E-2C46885C0F00}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{035A81E6-D0E9-4514-856A-4268F8CC9DA6}" name="SWRA" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{12D2C635-A485-47AD-8190-8C54FBF9000C}" name="Project" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{45F2C637-AC09-44A5-92E8-6BADCFC9B3F1}" name="Tasks" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{8FA9D5CD-8C7B-4804-B737-1E714122E0BB}" name="Bonus" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{2E8EFB19-CC52-4A38-A549-4773A4038088}" name="Table1012172213" displayName="Table1012172213" ref="B57:H58" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
-  <autoFilter ref="B57:H58" xr:uid="{2E8EFB19-CC52-4A38-A549-4773A4038088}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{B39D5E1C-69EB-4152-B8A8-1760D2448A90}" name="Linear Algebra" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{D10D149E-232F-4DAA-81C5-31D861839F41}" name="Quiz1" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{5CA6916F-5FA5-47DB-A9BD-91A639B91014}" name="Quiz1 Max" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{A3325A9B-02FB-4C53-B892-28DB2A463736}" name="Quiz2" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{44A6C65B-FA82-49DB-A3BB-780E2DED5ECE}" name="Quiz22" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{E6C766A9-E04E-4ADB-84CB-0183A38391BF}" name="Total" dataDxfId="41">
-      <calculatedColumnFormula>+Table1012172213[[#This Row],[Quiz1]]+Table1012172213[[#This Row],[Quiz2]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{89E4E1E6-96CC-4FF6-B9D1-52ECF82969B0}" name="Total Max" dataDxfId="40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{0C386865-EF18-4181-8C7E-093B513259C4}" name="Table10121721" displayName="Table10121721" ref="B45:G46" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+  <autoFilter ref="B45:G46" xr:uid="{0C386865-EF18-4181-8C7E-093B513259C4}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{42FC35EA-B43D-48B3-B3A3-595F88F92450}" name="Data Mining" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{9FEB74EB-AC46-401B-BB9E-8C8A45D5AF88}" name="Quiz" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{8B9598E1-5543-4747-9C5F-C4096AAF4F60}" name="Assignment 1" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{891DC4A3-A6EA-4A59-BA25-7BA469C2BB0A}" name="Assignment 2" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{758071D9-C1B0-45BD-B6BF-33C3918898F3}" name="Quiz 2" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{343E6371-5E31-41BB-B2F7-397D9E50F2F8}" name="Total" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{2207AA88-EE36-4624-A88E-6569E03C562E}" name="Table101217221325" displayName="Table101217221325" ref="B61:I62" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
-  <autoFilter ref="B61:I62" xr:uid="{2207AA88-EE36-4624-A88E-6569E03C562E}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A1410ADB-FBAA-48A1-A8DF-3A8B2E651D8B}" name="Opearting Systems" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{8776271C-5F25-4785-A95B-B458AEF6F282}" name="Quiz1" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{05E6A514-432C-455E-9251-B2B593D26098}" name="Quiz1 Max" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{36387145-7C98-4055-ABC2-E7AC4D91D251}" name="Quiz 2" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{F134A27C-6A58-4C39-A569-9F69227340DC}" name="Quiz2 Max" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{2E7E518B-2E59-4E43-8726-08526026E34B}" name="Report" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{6157D7A2-D60B-4F03-A097-7482D25F89D6}" name="Total" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{7547E26B-F008-458B-9456-6DEE8B7DB78B}" name="Total Max" dataDxfId="30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{7E679E8C-B166-4F68-9A53-21A0412D5E9D}" name="Table10121722" displayName="Table10121722" ref="B49:C50" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+  <autoFilter ref="B49:C50" xr:uid="{7E679E8C-B166-4F68-9A53-21A0412D5E9D}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{62817289-D4F9-4533-A45B-83BD78F1E21D}" name="Maths IV" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{85694941-D6AA-4481-BDF5-36CF8B4AE004}" name="Quiz" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{7EFEDB9D-732D-4630-8B03-7AFFC1AD7F0B}" name="Table101217221326" displayName="Table101217221326" ref="B65:G66" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="B65:G66" xr:uid="{7EFEDB9D-732D-4630-8B03-7AFFC1AD7F0B}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{186B9208-1B02-463B-927F-54C5F3F8ECA3}" name="Design and Analysis of Algorithms" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{5AF780C1-C46C-4238-A76A-BBE35D0DD3CE}" name="Quiz 1" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{C8A6FE4A-0A69-4C2A-A833-697D0B90F623}" name="Project" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{780FF1E4-AD54-4288-822A-14F698E383A9}" name="Total" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{B539CB65-6FBB-48BA-BF1A-D9899FE91DF1}" name="Total Max" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{7C2146AE-0FA2-490E-A979-F82977B2A392}" name="Bonus" dataDxfId="22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{2E8EFB19-CC52-4A38-A549-4773A4038088}" name="Table1012172213" displayName="Table1012172213" ref="B57:H58" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="B57:H58" xr:uid="{2E8EFB19-CC52-4A38-A549-4773A4038088}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{B39D5E1C-69EB-4152-B8A8-1760D2448A90}" name="Linear Algebra" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{D10D149E-232F-4DAA-81C5-31D861839F41}" name="Quiz1" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{5CA6916F-5FA5-47DB-A9BD-91A639B91014}" name="Quiz1 Max" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{A3325A9B-02FB-4C53-B892-28DB2A463736}" name="Quiz2" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{44A6C65B-FA82-49DB-A3BB-780E2DED5ECE}" name="Quiz22" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{E6C766A9-E04E-4ADB-84CB-0183A38391BF}" name="Total" dataDxfId="56">
+      <calculatedColumnFormula>+Table1012172213[[#This Row],[Quiz1]]+Table1012172213[[#This Row],[Quiz2]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{89E4E1E6-96CC-4FF6-B9D1-52ECF82969B0}" name="Total Max" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{DF7A8B39-9473-409F-BE6D-5CDCF065FCC9}" name="Table101217221327" displayName="Table101217221327" ref="B69:F70" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="B69:F70" xr:uid="{DF7A8B39-9473-409F-BE6D-5CDCF065FCC9}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{75F94FF8-2D45-4A55-99D4-4ED627023AFA}" name="Advanced Methods for Multimedia" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{88705062-D7C8-46E8-AA95-DAA631863958}" name="Sec Projects" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{F9618B6F-2F74-440B-9CF9-C226705955DC}" name="Sec Projects Max" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{4A66F216-977C-4163-B8CE-EDD7CBF7203B}" name="Lec Projects" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{DFE53239-C42B-4445-B658-06DB1051C764}" name="Lec Projects Max" dataDxfId="15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{2207AA88-EE36-4624-A88E-6569E03C562E}" name="Table101217221325" displayName="Table101217221325" ref="B61:I62" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+  <autoFilter ref="B61:I62" xr:uid="{2207AA88-EE36-4624-A88E-6569E03C562E}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{A1410ADB-FBAA-48A1-A8DF-3A8B2E651D8B}" name="Opearting Systems" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{8776271C-5F25-4785-A95B-B458AEF6F282}" name="Quiz1" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{05E6A514-432C-455E-9251-B2B593D26098}" name="Quiz1 Max" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{36387145-7C98-4055-ABC2-E7AC4D91D251}" name="Quiz 2" dataDxfId="49"/>
+    <tableColumn id="8" xr3:uid="{F134A27C-6A58-4C39-A569-9F69227340DC}" name="Quiz2 Max" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{2E7E518B-2E59-4E43-8726-08526026E34B}" name="Report" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{6157D7A2-D60B-4F03-A097-7482D25F89D6}" name="Total" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{7547E26B-F008-458B-9456-6DEE8B7DB78B}" name="Total Max" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{44CB78D9-9928-43D4-80DA-A73A09C1C177}" name="Table136" displayName="Table136" ref="B26:H34" totalsRowCount="1" headerRowDxfId="251" dataDxfId="250" totalsRowDxfId="249">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{44CB78D9-9928-43D4-80DA-A73A09C1C177}" name="Table136" displayName="Table136" ref="B26:H34" totalsRowCount="1" headerRowDxfId="276" dataDxfId="275" totalsRowDxfId="274">
   <autoFilter ref="B26:H33" xr:uid="{44CB78D9-9928-43D4-80DA-A73A09C1C177}"/>
   <tableColumns count="7">
-    <tableColumn id="8" xr3:uid="{80F5D784-25D0-41BF-B665-68DCCFC51EFF}" name="C. No" dataDxfId="248" totalsRowDxfId="247"/>
-    <tableColumn id="9" xr3:uid="{2B5580DF-E177-43F7-9479-7A8138AF1CE6}" name="Course Name" dataDxfId="246" totalsRowDxfId="245"/>
-    <tableColumn id="15" xr3:uid="{8ACB0870-3619-477D-A7D2-AA574B94DBD4}" name="Pre-Requisite" dataDxfId="244" totalsRowDxfId="243"/>
-    <tableColumn id="10" xr3:uid="{659372D5-C9CC-41E8-9569-93511561BC00}" name="Course Code" dataDxfId="242" totalsRowDxfId="241"/>
-    <tableColumn id="11" xr3:uid="{D56AECAB-5A16-435D-81B5-609A7D36AEBE}" name="Credit Hours" dataDxfId="240" totalsRowDxfId="239"/>
-    <tableColumn id="12" xr3:uid="{A1C5E82C-5836-4124-92EB-9BAFA5AF7757}" name="Credit Hour Price" dataDxfId="238" totalsRowDxfId="237"/>
-    <tableColumn id="13" xr3:uid="{5CF1FF64-9BF4-434F-8529-F1D78945F6AA}" name="Course Price" totalsRowFunction="sum" dataDxfId="236" totalsRowDxfId="235">
+    <tableColumn id="8" xr3:uid="{80F5D784-25D0-41BF-B665-68DCCFC51EFF}" name="C. No" dataDxfId="273" totalsRowDxfId="272"/>
+    <tableColumn id="9" xr3:uid="{2B5580DF-E177-43F7-9479-7A8138AF1CE6}" name="Course Name" dataDxfId="271" totalsRowDxfId="270"/>
+    <tableColumn id="15" xr3:uid="{8ACB0870-3619-477D-A7D2-AA574B94DBD4}" name="Pre-Requisite" dataDxfId="269" totalsRowDxfId="268"/>
+    <tableColumn id="10" xr3:uid="{659372D5-C9CC-41E8-9569-93511561BC00}" name="Course Code" dataDxfId="267" totalsRowDxfId="266"/>
+    <tableColumn id="11" xr3:uid="{D56AECAB-5A16-435D-81B5-609A7D36AEBE}" name="Credit Hours" dataDxfId="265" totalsRowDxfId="264"/>
+    <tableColumn id="12" xr3:uid="{A1C5E82C-5836-4124-92EB-9BAFA5AF7757}" name="Credit Hour Price" dataDxfId="263" totalsRowDxfId="262"/>
+    <tableColumn id="13" xr3:uid="{5CF1FF64-9BF4-434F-8529-F1D78945F6AA}" name="Course Price" totalsRowFunction="sum" dataDxfId="261" totalsRowDxfId="260">
       <calculatedColumnFormula array="1">MMULT(F27,G27)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2476,45 +2591,74 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{87AD0100-11F5-4429-A381-85314D0234F0}" name="Table101217221328" displayName="Table101217221328" ref="B73:F74" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
-  <autoFilter ref="B73:F74" xr:uid="{87AD0100-11F5-4429-A381-85314D0234F0}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A5601E5C-E375-40C5-97A4-E21B705AA075}" name="Intelligent Systems" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{2240AD9C-38F6-47C4-8BD5-EAEE10C04068}" name="Assignment" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{A14BA645-2253-4B09-B74C-057576947793}" name="Project" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{BDAE3480-C7EC-4F7C-878D-4C50E6262734}" name="Total" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{6C410047-0482-4545-9881-9931EE4C7F26}" name="Total Max" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{7EFEDB9D-732D-4630-8B03-7AFFC1AD7F0B}" name="Table101217221326" displayName="Table101217221326" ref="B65:G66" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
+  <autoFilter ref="B65:G66" xr:uid="{7EFEDB9D-732D-4630-8B03-7AFFC1AD7F0B}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{186B9208-1B02-463B-927F-54C5F3F8ECA3}" name="Design and Analysis of Algorithms" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{5AF780C1-C46C-4238-A76A-BBE35D0DD3CE}" name="Quiz 1" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{C8A6FE4A-0A69-4C2A-A833-697D0B90F623}" name="Project" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{780FF1E4-AD54-4288-822A-14F698E383A9}" name="Total" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{B539CB65-6FBB-48BA-BF1A-D9899FE91DF1}" name="Total Max" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{7C2146AE-0FA2-490E-A979-F82977B2A392}" name="Bonus" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2D7EAD71-4C91-43A3-A932-172CEEA55492}" name="Table101217221329" displayName="Table101217221329" ref="B77:G78" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{DF7A8B39-9473-409F-BE6D-5CDCF065FCC9}" name="Table101217221327" displayName="Table101217221327" ref="B69:F70" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35">
+  <autoFilter ref="B69:F70" xr:uid="{DF7A8B39-9473-409F-BE6D-5CDCF065FCC9}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{75F94FF8-2D45-4A55-99D4-4ED627023AFA}" name="Advanced Methods for Multimedia" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{88705062-D7C8-46E8-AA95-DAA631863958}" name="Sec Projects" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{F9618B6F-2F74-440B-9CF9-C226705955DC}" name="Sec Projects Max" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{4A66F216-977C-4163-B8CE-EDD7CBF7203B}" name="Lec Projects" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{DFE53239-C42B-4445-B658-06DB1051C764}" name="Lec Projects Max" dataDxfId="30"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{87AD0100-11F5-4429-A381-85314D0234F0}" name="Table101217221328" displayName="Table101217221328" ref="B73:F74" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="B73:F74" xr:uid="{87AD0100-11F5-4429-A381-85314D0234F0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A5601E5C-E375-40C5-97A4-E21B705AA075}" name="Intelligent Systems" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{2240AD9C-38F6-47C4-8BD5-EAEE10C04068}" name="Assignment" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{A14BA645-2253-4B09-B74C-057576947793}" name="Project" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{BDAE3480-C7EC-4F7C-878D-4C50E6262734}" name="Total" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{6C410047-0482-4545-9881-9931EE4C7F26}" name="Total Max" dataDxfId="23"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{2D7EAD71-4C91-43A3-A932-172CEEA55492}" name="Table101217221329" displayName="Table101217221329" ref="B77:G78" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="B77:G78" xr:uid="{2D7EAD71-4C91-43A3-A932-172CEEA55492}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{BD37413B-4A28-483D-9B6C-CA2468F72F8B}" name="Large-Scale Database" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{8ACAF496-83AE-4577-8105-E7F2D418F493}" name="Project 1" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{0AFE68A8-52C8-4747-BB8A-3B1C38E2BD7D}" name="Project 2" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{1BD72070-2E8A-4BBA-A175-C20D83CE3B45}" name="Assignment" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{EE08EFA1-C67A-468D-8D2C-6693EA6A1EED}" name="Total" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{2726B104-3C2D-4D50-852A-49C52478DDCE}" name="Total Max" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{BD37413B-4A28-483D-9B6C-CA2468F72F8B}" name="Large-Scale Database" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{8ACAF496-83AE-4577-8105-E7F2D418F493}" name="Project 1" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{0AFE68A8-52C8-4747-BB8A-3B1C38E2BD7D}" name="Project 2" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{1BD72070-2E8A-4BBA-A175-C20D83CE3B45}" name="Assignment" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{EE08EFA1-C67A-468D-8D2C-6693EA6A1EED}" name="Total" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{2726B104-3C2D-4D50-852A-49C52478DDCE}" name="Total Max" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D4355C40-4E02-42F5-988D-4A5436A373D3}" name="Table14" displayName="Table14" ref="B37:H44" totalsRowCount="1" headerRowDxfId="234" dataDxfId="233">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D4355C40-4E02-42F5-988D-4A5436A373D3}" name="Table14" displayName="Table14" ref="B37:H44" totalsRowCount="1" headerRowDxfId="259" dataDxfId="258">
   <autoFilter ref="B37:H43" xr:uid="{D4355C40-4E02-42F5-988D-4A5436A373D3}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E26A93C8-AE4E-414C-8609-4626D90048C7}" name="C. No" dataDxfId="232" totalsRowDxfId="231"/>
-    <tableColumn id="2" xr3:uid="{B98BD1A5-2AC7-4419-A1C4-41F460F6882C}" name="Course Name" dataDxfId="230" totalsRowDxfId="229"/>
-    <tableColumn id="3" xr3:uid="{D7ED69CE-3C3D-4DB9-AD04-D42ED613A7BE}" name="Pre-Requisite" dataDxfId="228" totalsRowDxfId="227"/>
-    <tableColumn id="4" xr3:uid="{9BD71A3A-3CD2-4155-8514-F83ED01B2573}" name="Course Code" dataDxfId="226" totalsRowDxfId="225"/>
-    <tableColumn id="5" xr3:uid="{2C63F556-3497-4C45-8DD5-70C18A6C1647}" name="Credit Hours" dataDxfId="224" totalsRowDxfId="223"/>
-    <tableColumn id="6" xr3:uid="{70C2C24E-CD3A-4255-B224-83BFBEC60F16}" name="Credit Hour Price" dataDxfId="222" totalsRowDxfId="221"/>
-    <tableColumn id="7" xr3:uid="{AAA5AB50-4647-403F-81FB-0DC834CB70A6}" name="Course Price" totalsRowFunction="custom" dataDxfId="220" totalsRowDxfId="219">
+    <tableColumn id="1" xr3:uid="{E26A93C8-AE4E-414C-8609-4626D90048C7}" name="C. No" dataDxfId="257" totalsRowDxfId="256"/>
+    <tableColumn id="2" xr3:uid="{B98BD1A5-2AC7-4419-A1C4-41F460F6882C}" name="Course Name" dataDxfId="255" totalsRowDxfId="254"/>
+    <tableColumn id="3" xr3:uid="{D7ED69CE-3C3D-4DB9-AD04-D42ED613A7BE}" name="Pre-Requisite" dataDxfId="253" totalsRowDxfId="252"/>
+    <tableColumn id="4" xr3:uid="{9BD71A3A-3CD2-4155-8514-F83ED01B2573}" name="Course Code" dataDxfId="251" totalsRowDxfId="250"/>
+    <tableColumn id="5" xr3:uid="{2C63F556-3497-4C45-8DD5-70C18A6C1647}" name="Credit Hours" dataDxfId="249" totalsRowDxfId="248"/>
+    <tableColumn id="6" xr3:uid="{70C2C24E-CD3A-4255-B224-83BFBEC60F16}" name="Credit Hour Price" dataDxfId="247" totalsRowDxfId="246"/>
+    <tableColumn id="7" xr3:uid="{AAA5AB50-4647-403F-81FB-0DC834CB70A6}" name="Course Price" totalsRowFunction="custom" dataDxfId="245" totalsRowDxfId="244">
       <calculatedColumnFormula array="1">MMULT(Table14[[#This Row],[Credit Hours]],Table14[[#This Row],[Credit Hour Price]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109, Table14[Course Price])</totalsRowFormula>
     </tableColumn>
@@ -2524,16 +2668,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5BF30FC0-0DED-469F-97BB-4489B34E0B57}" name="Table1368" displayName="Table1368" ref="B47:H54" totalsRowCount="1" headerRowDxfId="218" dataDxfId="217" totalsRowDxfId="216">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5BF30FC0-0DED-469F-97BB-4489B34E0B57}" name="Table1368" displayName="Table1368" ref="B47:H54" totalsRowCount="1" headerRowDxfId="243" dataDxfId="242" totalsRowDxfId="241">
   <autoFilter ref="B47:H53" xr:uid="{5BF30FC0-0DED-469F-97BB-4489B34E0B57}"/>
   <tableColumns count="7">
-    <tableColumn id="8" xr3:uid="{B64828CC-70B6-481E-8751-040DCF13806C}" name="C. No" dataDxfId="215" totalsRowDxfId="214"/>
-    <tableColumn id="9" xr3:uid="{517C09CB-5A48-4E23-B313-E12769E4DC0D}" name="Course Name" dataDxfId="213" totalsRowDxfId="212"/>
-    <tableColumn id="15" xr3:uid="{53AA2425-9B1D-4591-967B-465C4326D099}" name="Pre-Requisite" dataDxfId="211" totalsRowDxfId="210"/>
-    <tableColumn id="10" xr3:uid="{578A44FF-83C6-47CA-8B00-60A563C3EEF0}" name="Course Code" dataDxfId="209" totalsRowDxfId="208"/>
-    <tableColumn id="11" xr3:uid="{D9C7FA6F-EAA5-4DE5-8954-FA3BE0F4B246}" name="Credit Hours" dataDxfId="207" totalsRowDxfId="206"/>
-    <tableColumn id="12" xr3:uid="{990CB230-10C5-486C-B992-EB264F34C368}" name="Credit Hour Price" dataDxfId="205" totalsRowDxfId="204"/>
-    <tableColumn id="13" xr3:uid="{C0CAE4D3-081F-4843-87AB-C9EF38854009}" name="Course Price" totalsRowFunction="sum" dataDxfId="203" totalsRowDxfId="202">
+    <tableColumn id="8" xr3:uid="{B64828CC-70B6-481E-8751-040DCF13806C}" name="C. No" dataDxfId="240" totalsRowDxfId="239"/>
+    <tableColumn id="9" xr3:uid="{517C09CB-5A48-4E23-B313-E12769E4DC0D}" name="Course Name" dataDxfId="238" totalsRowDxfId="237"/>
+    <tableColumn id="15" xr3:uid="{53AA2425-9B1D-4591-967B-465C4326D099}" name="Pre-Requisite" dataDxfId="236" totalsRowDxfId="235"/>
+    <tableColumn id="10" xr3:uid="{578A44FF-83C6-47CA-8B00-60A563C3EEF0}" name="Course Code" dataDxfId="234" totalsRowDxfId="233"/>
+    <tableColumn id="11" xr3:uid="{D9C7FA6F-EAA5-4DE5-8954-FA3BE0F4B246}" name="Credit Hours" dataDxfId="232" totalsRowDxfId="231"/>
+    <tableColumn id="12" xr3:uid="{990CB230-10C5-486C-B992-EB264F34C368}" name="Credit Hour Price" dataDxfId="230" totalsRowDxfId="229"/>
+    <tableColumn id="13" xr3:uid="{C0CAE4D3-081F-4843-87AB-C9EF38854009}" name="Course Price" totalsRowFunction="sum" dataDxfId="228" totalsRowDxfId="227">
       <calculatedColumnFormula array="1">MMULT(F48,G48)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2542,16 +2686,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{225A79AA-1E6C-4A25-843E-BF1C506DE0BB}" name="Table136823" displayName="Table136823" ref="B57:H65" totalsRowCount="1" headerRowDxfId="201" dataDxfId="200" totalsRowDxfId="199">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{225A79AA-1E6C-4A25-843E-BF1C506DE0BB}" name="Table136823" displayName="Table136823" ref="B57:H65" totalsRowCount="1" headerRowDxfId="226" dataDxfId="225" totalsRowDxfId="224">
   <autoFilter ref="B57:H64" xr:uid="{225A79AA-1E6C-4A25-843E-BF1C506DE0BB}"/>
   <tableColumns count="7">
-    <tableColumn id="8" xr3:uid="{9E17818D-FB4E-4444-8590-E7CF360518AF}" name="C. No" dataDxfId="198" totalsRowDxfId="197"/>
-    <tableColumn id="9" xr3:uid="{5428B2D8-86E9-43F1-AAE5-8F72ECE9F637}" name="Course Name" dataDxfId="196" totalsRowDxfId="195"/>
-    <tableColumn id="15" xr3:uid="{4815685E-33A4-4920-AA6A-B7C0DF7839BD}" name="Pre-Requisite" dataDxfId="194" totalsRowDxfId="193"/>
-    <tableColumn id="10" xr3:uid="{9D5102A6-5623-47CE-B2F1-46B015CBEA1F}" name="Course Code" dataDxfId="192" totalsRowDxfId="191"/>
-    <tableColumn id="11" xr3:uid="{6FD41B09-EE2D-48E9-B293-6EDB777171FC}" name="Credit Hours" dataDxfId="190" totalsRowDxfId="189"/>
-    <tableColumn id="12" xr3:uid="{657345A1-4DB2-429D-A3FB-A24319E3C23F}" name="Credit Hour Price" dataDxfId="188" totalsRowDxfId="187"/>
-    <tableColumn id="13" xr3:uid="{2E889CCC-7B1F-4A1F-AC7D-A2647F18ACAB}" name="Course Price" totalsRowFunction="sum" dataDxfId="186" totalsRowDxfId="185">
+    <tableColumn id="8" xr3:uid="{9E17818D-FB4E-4444-8590-E7CF360518AF}" name="C. No" dataDxfId="223" totalsRowDxfId="222"/>
+    <tableColumn id="9" xr3:uid="{5428B2D8-86E9-43F1-AAE5-8F72ECE9F637}" name="Course Name" dataDxfId="221" totalsRowDxfId="220"/>
+    <tableColumn id="15" xr3:uid="{4815685E-33A4-4920-AA6A-B7C0DF7839BD}" name="Pre-Requisite" dataDxfId="219" totalsRowDxfId="218"/>
+    <tableColumn id="10" xr3:uid="{9D5102A6-5623-47CE-B2F1-46B015CBEA1F}" name="Course Code" dataDxfId="217" totalsRowDxfId="216"/>
+    <tableColumn id="11" xr3:uid="{6FD41B09-EE2D-48E9-B293-6EDB777171FC}" name="Credit Hours" dataDxfId="215" totalsRowDxfId="214"/>
+    <tableColumn id="12" xr3:uid="{657345A1-4DB2-429D-A3FB-A24319E3C23F}" name="Credit Hour Price" dataDxfId="213" totalsRowDxfId="212"/>
+    <tableColumn id="13" xr3:uid="{2E889CCC-7B1F-4A1F-AC7D-A2647F18ACAB}" name="Course Price" totalsRowFunction="sum" dataDxfId="211" totalsRowDxfId="210">
       <calculatedColumnFormula array="1">MMULT(F58,G58)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2560,16 +2704,16 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{DEE2F87F-3551-4DE0-8BF1-90791BE9A6FB}" name="Table136831" displayName="Table136831" ref="B68:H75" totalsRowCount="1" headerRowDxfId="184" dataDxfId="183" totalsRowDxfId="182">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{DEE2F87F-3551-4DE0-8BF1-90791BE9A6FB}" name="Table136831" displayName="Table136831" ref="B68:H75" totalsRowCount="1" headerRowDxfId="209" dataDxfId="208" totalsRowDxfId="207">
   <autoFilter ref="B68:H74" xr:uid="{DEE2F87F-3551-4DE0-8BF1-90791BE9A6FB}"/>
   <tableColumns count="7">
-    <tableColumn id="8" xr3:uid="{41546DFE-1DDF-40DB-89A2-0A850946FDF9}" name="C. No" dataDxfId="181" totalsRowDxfId="180"/>
-    <tableColumn id="9" xr3:uid="{D9805A40-FF2A-456B-BEFF-3DE682224242}" name="Course Name" dataDxfId="179" totalsRowDxfId="178"/>
-    <tableColumn id="15" xr3:uid="{F1FE5352-1709-4DB4-A6C7-7652CE05B31A}" name="Pre-Requisite" dataDxfId="177" totalsRowDxfId="176"/>
-    <tableColumn id="10" xr3:uid="{9BA5F390-1523-4AE6-986F-3CAB515A9136}" name="Course Code" dataDxfId="175" totalsRowDxfId="174"/>
-    <tableColumn id="11" xr3:uid="{3F3509AF-0737-406F-AB6E-D7EAA4991C20}" name="Credit Hours" dataDxfId="173" totalsRowDxfId="172"/>
-    <tableColumn id="12" xr3:uid="{358C9C4B-F156-4D27-BC56-09AD6B6C57CC}" name="Credit Hour Price" dataDxfId="171" totalsRowDxfId="170"/>
-    <tableColumn id="13" xr3:uid="{4BCE169B-CD06-4757-A27B-B9D3121D3017}" name="Course Price" totalsRowFunction="sum" dataDxfId="169" totalsRowDxfId="168">
+    <tableColumn id="8" xr3:uid="{41546DFE-1DDF-40DB-89A2-0A850946FDF9}" name="C. No" dataDxfId="206" totalsRowDxfId="205"/>
+    <tableColumn id="9" xr3:uid="{D9805A40-FF2A-456B-BEFF-3DE682224242}" name="Course Name" dataDxfId="204" totalsRowDxfId="203"/>
+    <tableColumn id="15" xr3:uid="{F1FE5352-1709-4DB4-A6C7-7652CE05B31A}" name="Pre-Requisite" dataDxfId="202" totalsRowDxfId="201"/>
+    <tableColumn id="10" xr3:uid="{9BA5F390-1523-4AE6-986F-3CAB515A9136}" name="Course Code" dataDxfId="200" totalsRowDxfId="199"/>
+    <tableColumn id="11" xr3:uid="{3F3509AF-0737-406F-AB6E-D7EAA4991C20}" name="Credit Hours" dataDxfId="198" totalsRowDxfId="197"/>
+    <tableColumn id="12" xr3:uid="{358C9C4B-F156-4D27-BC56-09AD6B6C57CC}" name="Credit Hour Price" dataDxfId="196" totalsRowDxfId="195"/>
+    <tableColumn id="13" xr3:uid="{4BCE169B-CD06-4757-A27B-B9D3121D3017}" name="Course Price" totalsRowFunction="sum" dataDxfId="194" totalsRowDxfId="193">
       <calculatedColumnFormula array="1">MMULT(F69,G69)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2578,30 +2722,32 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7AFF9129-6ACC-422A-A110-9760E0DB5968}" name="Table3" displayName="Table3" ref="B4:F11" totalsRowShown="0" dataDxfId="167">
-  <autoFilter ref="B4:F11" xr:uid="{7AFF9129-6ACC-422A-A110-9760E0DB5968}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{47BB9116-96B6-4659-B8C9-6763DFE5D1EB}" name="S. No" dataDxfId="166"/>
-    <tableColumn id="2" xr3:uid="{2B8CF846-525A-49A3-A6F6-814996D28C49}" name="Course Name" dataDxfId="165"/>
-    <tableColumn id="3" xr3:uid="{B231F6C5-4575-494A-8370-72E0D3EDCBDC}" name="Midterm" dataDxfId="164"/>
-    <tableColumn id="4" xr3:uid="{D6654B14-A53B-4F5A-9499-ECE1E8712304}" name="Pre-Final" dataDxfId="163"/>
-    <tableColumn id="5" xr3:uid="{EAE2A77F-EEAE-4EFE-9A61-3E4A9E141D71}" name="Final" dataDxfId="162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{DE5B5BA3-848C-46B4-9F48-F03850E0DF7B}" name="Table13682333" displayName="Table13682333" ref="B78:H83" totalsRowCount="1" headerRowDxfId="192" dataDxfId="191" totalsRowDxfId="190">
+  <autoFilter ref="B78:H82" xr:uid="{DE5B5BA3-848C-46B4-9F48-F03850E0DF7B}"/>
+  <tableColumns count="7">
+    <tableColumn id="8" xr3:uid="{D95091D6-D168-42F9-B2D7-95276F8E5242}" name="C. No" dataDxfId="189" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{87EF14CB-745D-43D4-B1B3-B09E82C7B429}" name="Course Name" dataDxfId="188" totalsRowDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{AEB2ED9C-BD07-4087-AA0C-E23D1B55C6CA}" name="Pre-Requisite" dataDxfId="187" totalsRowDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{28BF7965-2285-4550-A6EC-84066169277D}" name="Course Code" dataDxfId="186" totalsRowDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{E877E3BB-E79B-4814-9EE1-299C19854CCC}" name="Credit Hours" dataDxfId="185" totalsRowDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{4ACDE9D9-EC0E-4C46-83BF-FDE93753D076}" name="Credit Hour Price" dataDxfId="184" totalsRowDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{815960C1-45D1-4B52-887C-60D71612ABE7}" name="Course Price" totalsRowFunction="sum" dataDxfId="183" totalsRowDxfId="0">
+      <calculatedColumnFormula array="1">MMULT(F79,G79)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{70147C35-1E51-4E8F-8D2F-0DC595D09A6B}" name="Table35" displayName="Table35" ref="B15:H22" totalsRowShown="0" dataDxfId="161">
-  <autoFilter ref="B15:H22" xr:uid="{70147C35-1E51-4E8F-8D2F-0DC595D09A6B}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{02190C55-16B9-496A-8C2B-E2D76168AF93}" name="S. No" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{8DDC9744-D783-4D5E-B711-CF5C3C040ABC}" name="Course Name" dataDxfId="159"/>
-    <tableColumn id="4" xr3:uid="{34FCA559-C89D-473C-8942-2292B887A2A4}" name="Midterm" dataDxfId="158"/>
-    <tableColumn id="11" xr3:uid="{26BFE13A-C341-4990-AFFA-A6ECAD09F356}" name="Pre-Final" dataDxfId="157"/>
-    <tableColumn id="12" xr3:uid="{BCC3D8B0-331D-4A91-B469-53D9E53C629B}" name="Final" dataDxfId="156"/>
-    <tableColumn id="3" xr3:uid="{AAF2F08F-0FFC-4D29-8E35-7A389C090684}" name="Bonus" dataDxfId="155"/>
-    <tableColumn id="5" xr3:uid="{6B12A4D2-2FF5-4394-9DE7-26EFEC40F165}" name="Project" dataDxfId="154"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7AFF9129-6ACC-422A-A110-9760E0DB5968}" name="Table3" displayName="Table3" ref="B4:F11" totalsRowShown="0" dataDxfId="182">
+  <autoFilter ref="B4:F11" xr:uid="{7AFF9129-6ACC-422A-A110-9760E0DB5968}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{47BB9116-96B6-4659-B8C9-6763DFE5D1EB}" name="S. No" dataDxfId="181"/>
+    <tableColumn id="2" xr3:uid="{2B8CF846-525A-49A3-A6F6-814996D28C49}" name="Course Name" dataDxfId="180"/>
+    <tableColumn id="3" xr3:uid="{B231F6C5-4575-494A-8370-72E0D3EDCBDC}" name="Midterm" dataDxfId="179"/>
+    <tableColumn id="4" xr3:uid="{D6654B14-A53B-4F5A-9499-ECE1E8712304}" name="Pre-Final" dataDxfId="178"/>
+    <tableColumn id="5" xr3:uid="{EAE2A77F-EEAE-4EFE-9A61-3E4A9E141D71}" name="Final" dataDxfId="177"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2954,7 +3100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CFA252-092A-4B93-AE8C-B7C35D64BCB8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16.21875" style="8" bestFit="1" customWidth="1"/>
@@ -2976,7 +3122,7 @@
       </c>
       <c r="C1" s="35">
         <f>SUBTOTAL(9,F:F)</f>
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>163</v>
@@ -4314,6 +4460,140 @@
       <c r="H75" s="8">
         <f>SUBTOTAL(109,Table136831[Course Price])</f>
         <v>17000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B78" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B79" s="8">
+        <v>1</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E79" s="7">
+        <v>4170410</v>
+      </c>
+      <c r="F79" s="8">
+        <v>3</v>
+      </c>
+      <c r="G79" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H79" s="8" cm="1">
+        <f t="array" ref="H79">MMULT(F79,G79)</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B80" s="8">
+        <v>2</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E80" s="7">
+        <v>4170402</v>
+      </c>
+      <c r="F80" s="8">
+        <v>3</v>
+      </c>
+      <c r="G80" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H80" s="8" cm="1">
+        <f t="array" ref="H80">MMULT(F80,G80)</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" s="8">
+        <v>3</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E81" s="7">
+        <v>4170309</v>
+      </c>
+      <c r="F81" s="8">
+        <v>3</v>
+      </c>
+      <c r="G81" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H81" s="8" cm="1">
+        <f t="array" ref="H81">MMULT(F81,G81)</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B82" s="8">
+        <v>4</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E82" s="7">
+        <v>4170408</v>
+      </c>
+      <c r="F82" s="8">
+        <v>3</v>
+      </c>
+      <c r="G82" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H82" s="8" cm="1">
+        <f t="array" ref="H82">MMULT(F82,G82)</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D83" s="8"/>
+      <c r="H83" s="8">
+        <f>SUBTOTAL(109,Table13682333[Course Price])</f>
+        <v>12000</v>
       </c>
     </row>
   </sheetData>
@@ -4326,17 +4606,19 @@
     <hyperlink ref="A46" location="Grades!B46" display="Grades" xr:uid="{FC3E8CC9-90D6-4316-828D-9BDABDD9C319}"/>
     <hyperlink ref="A56" location="Grades!B56" display="Grades" xr:uid="{1D39CBA0-4DA2-4250-A411-C509FB080175}"/>
     <hyperlink ref="A67" location="Grades!B67" display="Grades" xr:uid="{EE89FEBE-4EA8-41A9-80B6-80751E7549DD}"/>
+    <hyperlink ref="A77" r:id="rId1" location="Grades!B77" xr:uid="{DAEFD0C4-4420-4EBA-A963-EEE614B079BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="7">
-    <tablePart r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <tableParts count="8">
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4344,7 +4626,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F5D615-ABF8-45A5-A4C3-80C40388C6BC}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
@@ -5648,6 +5930,126 @@
       <c r="H74" s="21" t="s">
         <v>25</v>
       </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G78" t="s">
+        <v>137</v>
+      </c>
+      <c r="H78" t="s">
+        <v>24</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="4"/>
+      <c r="B79" s="20">
+        <v>1</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="21"/>
+      <c r="J79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="20">
+        <v>2</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="21"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B81" s="20">
+        <v>3</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="21"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B82" s="20">
+        <v>4</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="21"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="4"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="21"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="4"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5685,28 +6087,32 @@
     <hyperlink ref="A73" r:id="rId22" location="Details!A132" xr:uid="{AA596E71-3FD0-4FC3-8270-4D2A2C114B08}"/>
     <hyperlink ref="A70" r:id="rId23" location="Details!A120" xr:uid="{AC5AFA51-6E15-4EC2-8530-823D35EA4D3F}"/>
     <hyperlink ref="A69" r:id="rId24" location="Details!A116" xr:uid="{67CA2FD1-B2E1-449D-8C5D-9E8B013BC53E}"/>
+    <hyperlink ref="A81" r:id="rId25" location="Details!A148" xr:uid="{83BC74DA-D95A-409E-B64A-0BD76347B823}"/>
+    <hyperlink ref="A82" r:id="rId26" location="Details!A152" xr:uid="{1BA1FA74-E888-4E8C-A0A1-696BDECD3F84}"/>
+    <hyperlink ref="A80" r:id="rId27" location="Details!A144" xr:uid="{FF5D57A8-2CB3-46FC-8AB7-AE774B27FFE3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId25"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
   <ignoredErrors>
     <ignoredError sqref="D20" twoDigitTextYear="1"/>
     <ignoredError sqref="F48:F53" calculatedColumn="1"/>
   </ignoredErrors>
-  <tableParts count="7">
-    <tablePart r:id="rId26"/>
-    <tablePart r:id="rId27"/>
-    <tablePart r:id="rId28"/>
+  <tableParts count="8">
     <tablePart r:id="rId29"/>
     <tablePart r:id="rId30"/>
     <tablePart r:id="rId31"/>
     <tablePart r:id="rId32"/>
+    <tablePart r:id="rId33"/>
+    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId35"/>
+    <tablePart r:id="rId36"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0A9952D-2478-4AE3-A0CE-BBC1B333A118}">
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.44140625" style="8" bestFit="1" customWidth="1"/>
@@ -6940,6 +7346,83 @@
       <c r="G138" s="25">
         <v>1</v>
       </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B145" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C145" s="31"/>
+      <c r="D145" s="31"/>
+      <c r="E145" s="31"/>
+      <c r="F145" s="31"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B146" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C146" s="25"/>
+      <c r="D146" s="25"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="25"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="10" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B149" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="C149" s="31"/>
+      <c r="D149" s="31"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B150" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C150" s="25"/>
+      <c r="D150" s="25"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B153" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C153" s="31"/>
+      <c r="D153" s="31"/>
+      <c r="E153" s="31"/>
+      <c r="F153" s="31"/>
+      <c r="G153" s="31"/>
+      <c r="H153" s="31"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B154" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C154" s="25"/>
+      <c r="D154" s="25"/>
+      <c r="E154" s="25"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="25"/>
+      <c r="H154" s="25"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6969,11 +7452,13 @@
     <hyperlink ref="A128" location="Grades!C72" display="System Simulation and Modeling" xr:uid="{1A7CF686-4F82-4B82-899B-DA403FC894CC}"/>
     <hyperlink ref="A132" location="Grades!C73" display="Software Analysis and Verification" xr:uid="{0AFFABA2-2E15-4033-8743-5CC08809C5F0}"/>
     <hyperlink ref="A136" location="Grades!C74" display="Project Management" xr:uid="{3D2C0F12-D6A7-49F7-B43C-7D1828537CA1}"/>
+    <hyperlink ref="A144" r:id="rId2" location="Grades!C80" xr:uid="{0042A8B7-DA05-4B40-AFC4-08E992A4C7FE}"/>
+    <hyperlink ref="A148" location="Grades!C81" display="User Interface Design" xr:uid="{8DF5F7BB-1CF5-462F-9B38-0CB3501901B5}"/>
+    <hyperlink ref="A152" location="Grades!C82" display="Information Retrieval" xr:uid="{222FDC56-49C3-4326-998F-DECB005B0A9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
   <tableParts count="17">
-    <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
@@ -6990,6 +7475,7 @@
     <tablePart r:id="rId17"/>
     <tablePart r:id="rId18"/>
     <tablePart r:id="rId19"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
